--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_aysen.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_aysen.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>28.43828414386426</v>
+      </c>
+      <c r="C2">
         <v>26.9900824471263</v>
-      </c>
-      <c r="C2">
-        <v>28.43828414386426</v>
       </c>
       <c r="D2">
         <v>3.705064636089959</v>
       </c>
       <c r="E2">
-        <v>17.36496563600302</v>
+        <v>18.29671427912483</v>
       </c>
       <c r="F2">
         <v>64.33832008487215</v>
       </c>
       <c r="G2">
-        <v>18.29671427912483</v>
+        <v>17.36496563600302</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>22.9957805907173</v>
+      </c>
+      <c r="C3">
         <v>42.40506329113924</v>
-      </c>
-      <c r="C3">
-        <v>22.9957805907173</v>
       </c>
       <c r="D3">
         <v>2.358208955223881</v>
       </c>
       <c r="E3">
-        <v>25.63775510204081</v>
+        <v>13.9030612244898</v>
       </c>
       <c r="F3">
         <v>60.45918367346939</v>
       </c>
       <c r="G3">
-        <v>13.9030612244898</v>
+        <v>25.63775510204081</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>27.4368426759189</v>
+      </c>
+      <c r="C4">
         <v>26.26585709638946</v>
-      </c>
-      <c r="C4">
-        <v>27.4368426759189</v>
       </c>
       <c r="D4">
         <v>3.807223942208462</v>
       </c>
       <c r="E4">
-        <v>17.08874153498871</v>
+        <v>17.85059255079007</v>
       </c>
       <c r="F4">
         <v>65.06066591422122</v>
       </c>
       <c r="G4">
-        <v>17.85059255079007</v>
+        <v>17.08874153498871</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>26.0217654171705</v>
+      </c>
+      <c r="C5">
         <v>25.53808948004836</v>
-      </c>
-      <c r="C5">
-        <v>26.0217654171705</v>
       </c>
       <c r="D5">
         <v>3.915719696969697</v>
       </c>
       <c r="E5">
-        <v>16.85016754427956</v>
+        <v>17.16929950534546</v>
       </c>
       <c r="F5">
         <v>65.98053295037498</v>
       </c>
       <c r="G5">
-        <v>17.16929950534546</v>
+        <v>16.85016754427956</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.57884427032321</v>
+      </c>
+      <c r="C6">
         <v>22.91870714985308</v>
-      </c>
-      <c r="C6">
-        <v>29.57884427032321</v>
       </c>
       <c r="D6">
         <v>4.363247863247863</v>
       </c>
       <c r="E6">
-        <v>15.02890173410405</v>
+        <v>19.39627488760437</v>
       </c>
       <c r="F6">
         <v>65.5748233782916</v>
       </c>
       <c r="G6">
-        <v>19.39627488760437</v>
+        <v>15.02890173410405</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>29.58057395143488</v>
+      </c>
+      <c r="C7">
         <v>28.07211184694629</v>
-      </c>
-      <c r="C7">
-        <v>29.58057395143488</v>
       </c>
       <c r="D7">
         <v>3.562254259501966</v>
       </c>
       <c r="E7">
-        <v>17.80630105017503</v>
+        <v>18.76312718786465</v>
       </c>
       <c r="F7">
         <v>63.43057176196033</v>
       </c>
       <c r="G7">
-        <v>18.76312718786465</v>
+        <v>17.80630105017503</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>19.88795518207283</v>
+      </c>
+      <c r="C8">
         <v>6.442577030812324</v>
-      </c>
-      <c r="C8">
-        <v>19.88795518207283</v>
       </c>
       <c r="D8">
         <v>15.52173913043478</v>
       </c>
       <c r="E8">
-        <v>5.099778270509977</v>
+        <v>15.74279379157428</v>
       </c>
       <c r="F8">
         <v>79.15742793791574</v>
       </c>
       <c r="G8">
-        <v>15.74279379157428</v>
+        <v>5.099778270509977</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>33.5243553008596</v>
+      </c>
+      <c r="C9">
         <v>20.05730659025788</v>
-      </c>
-      <c r="C9">
-        <v>33.5243553008596</v>
       </c>
       <c r="D9">
         <v>4.985714285714286</v>
       </c>
       <c r="E9">
-        <v>13.05970149253731</v>
+        <v>21.82835820895522</v>
       </c>
       <c r="F9">
         <v>65.11194029850746</v>
       </c>
       <c r="G9">
-        <v>21.82835820895522</v>
+        <v>13.05970149253731</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>25.66322256352974</v>
+      </c>
+      <c r="C10">
         <v>40.63110862887462</v>
-      </c>
-      <c r="C10">
-        <v>25.66322256352974</v>
       </c>
       <c r="D10">
         <v>2.461168384879725</v>
       </c>
       <c r="E10">
+        <v>15.43240973971453</v>
+      </c>
+      <c r="F10">
+        <v>60.13434089000839</v>
+      </c>
+      <c r="G10">
         <v>24.43324937027708</v>
-      </c>
-      <c r="F10">
-        <v>60.1343408900084</v>
-      </c>
-      <c r="G10">
-        <v>15.43240973971453</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>20.45863309352518</v>
+      </c>
+      <c r="C11">
         <v>38.1294964028777</v>
-      </c>
-      <c r="C11">
-        <v>20.45863309352518</v>
       </c>
       <c r="D11">
         <v>2.622641509433962</v>
       </c>
       <c r="E11">
-        <v>24.04309611567905</v>
+        <v>12.90048199603062</v>
       </c>
       <c r="F11">
         <v>63.05642188829034</v>
       </c>
       <c r="G11">
-        <v>12.90048199603062</v>
+        <v>24.04309611567905</v>
       </c>
     </row>
   </sheetData>
